--- a/lab4.xlsx
+++ b/lab4.xlsx
@@ -1,69 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\atomg\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30A6832-0B87-44C0-AC74-C9B76B540FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{E69A349C-DB63-4430-9DD4-933CC0954894}"/>
   </bookViews>
   <sheets>
-    <sheet name="3.1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="3.1" sheetId="3" r:id="rId1"/>
+    <sheet name="3.2" sheetId="1" r:id="rId2"/>
+    <sheet name="3.3" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
-    <t xml:space="preserve">x</t>
+    <t>x</t>
   </si>
   <si>
-    <t xml:space="preserve">y</t>
+    <t>y</t>
   </si>
   <si>
-    <t xml:space="preserve">9,7</t>
+    <t>TREND</t>
+  </si>
+  <si>
+    <t>FORECAST</t>
+  </si>
+  <si>
+    <t>GROWTH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -74,16 +111,24 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
     <font>
-      <sz val="13"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -94,174 +139,127 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="3">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="3">
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{5D87EDA0-6A66-4D54-9830-22721C8986DC}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{1FC5272C-5922-4B7F-9996-F6113607AACC}"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFB3B3B3"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF004586"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:rPr>
+              <a:rPr lang="en-US"/>
               <a:t>Linear</a:t>
             </a:r>
           </a:p>
@@ -270,13 +268,35 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -295,74 +315,76 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:ln w="28800">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                 </a:ln>
+                <a:effectLst/>
               </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="004586"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'3.1'!$B$1:$P$1</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -416,7 +438,7 @@
             <c:numRef>
               <c:f>'3.1'!$B$2:$P$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.4</c:v>
@@ -440,7 +462,7 @@
                   <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.1</c:v>
@@ -450,6 +472,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.2</c:v>
@@ -464,46 +489,87 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-806C-44BC-BF8A-5E6BAF4B7B9C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="75729470"/>
-        <c:axId val="61144724"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="904582560"/>
+        <c:axId val="904582144"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="75729470"/>
+        <c:axId val="904582560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61144724"/>
+        <c:crossAx val="904582144"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="61144724"/>
+        <c:axId val="904582144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -511,107 +577,146 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75729470"/>
+        <c:crossAx val="904582560"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="span"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:rPr>
+              <a:rPr lang="en-US"/>
               <a:t>Logarithmic</a:t>
             </a:r>
           </a:p>
@@ -620,13 +725,35 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -645,74 +772,76 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="log"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:ln w="28800">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                 </a:ln>
+                <a:effectLst/>
               </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="004586"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="log"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'3.1'!$B$1:$P$1</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -766,7 +895,7 @@
             <c:numRef>
               <c:f>'3.1'!$B$2:$P$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.4</c:v>
@@ -790,7 +919,7 @@
                   <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.1</c:v>
@@ -800,6 +929,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.2</c:v>
@@ -814,46 +946,87 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-06E7-4B4E-AFE0-6FA549FE69F6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="86352100"/>
-        <c:axId val="34291299"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1466738048"/>
+        <c:axId val="1466733056"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="86352100"/>
+        <c:axId val="1466738048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34291299"/>
+        <c:crossAx val="1466733056"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="34291299"/>
+        <c:axId val="1466733056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -861,108 +1034,147 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86352100"/>
+        <c:crossAx val="1466738048"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="span"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Exponential</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Power</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -970,13 +1182,35 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -995,74 +1229,76 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="power"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:ln w="28800">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                 </a:ln>
+                <a:effectLst/>
               </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="004586"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="exp"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'3.1'!$B$1:$P$1</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1116,7 +1352,7 @@
             <c:numRef>
               <c:f>'3.1'!$B$2:$P$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.4</c:v>
@@ -1140,7 +1376,7 @@
                   <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.1</c:v>
@@ -1150,6 +1386,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.2</c:v>
@@ -1164,46 +1403,87 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A92C-4645-9F81-96E2E0ACBC5C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="72572759"/>
-        <c:axId val="23201735"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1438451808"/>
+        <c:axId val="1438438080"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="72572759"/>
+        <c:axId val="1438451808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23201735"/>
+        <c:crossAx val="1438438080"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="23201735"/>
+        <c:axId val="1438438080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1211,108 +1491,147 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72572759"/>
+        <c:crossAx val="1438451808"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="span"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Power</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Polynomial</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1320,13 +1639,35 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1345,74 +1686,77 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="6"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:ln w="28800">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                 </a:ln>
+                <a:effectLst/>
               </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="004586"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="power"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'3.1'!$B$1:$P$1</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1466,7 +1810,7 @@
             <c:numRef>
               <c:f>'3.1'!$B$2:$P$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.4</c:v>
@@ -1490,7 +1834,7 @@
                   <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.1</c:v>
@@ -1500,6 +1844,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.2</c:v>
@@ -1514,46 +1861,87 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-536E-4A9B-860D-F9E6E82DA3EC}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="5866597"/>
-        <c:axId val="12056036"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1466724976"/>
+        <c:axId val="1466725392"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="5866597"/>
+        <c:axId val="1466724976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="12056036"/>
+        <c:crossAx val="1466725392"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="12056036"/>
+        <c:axId val="1466725392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1561,108 +1949,147 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5866597"/>
+        <c:crossAx val="1466724976"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
-          </a:solidFill>
+        <a:ln>
+          <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="span"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1300" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:rPr>
-              <a:t>Polynomial</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Exponential</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1670,13 +2097,35 @@
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
-        <a:ln w="0">
+        <a:ln>
           <a:noFill/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1695,75 +2144,76 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="004586"/>
-            </a:solidFill>
-            <a:ln w="28800">
+            <a:ln w="19050" cap="rnd">
               <a:noFill/>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="square"/>
-            <c:size val="8"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="none"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
-                <a:ln w="28800">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                 </a:ln>
+                <a:effectLst/>
               </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="0">
-                <a:solidFill>
-                  <a:srgbClr val="004586"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-            <c:trendlineType val="poly"/>
-            <c:order val="6"/>
-            <c:forward val="0"/>
-            <c:backward val="0"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
           </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'3.1'!$B$1:$P$1</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
@@ -1817,7 +2267,7 @@
             <c:numRef>
               <c:f>'3.1'!$B$2:$P$2</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>3.4</c:v>
@@ -1841,7 +2291,7 @@
                   <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.2</c:v>
+                  <c:v>8.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>9.1</c:v>
@@ -1851,6 +2301,9 @@
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>11.2</c:v>
@@ -1865,46 +2318,87 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B452-434D-B19B-862F40F0BFF0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
-        <c:axId val="94707838"/>
-        <c:axId val="95963334"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1084531472"/>
+        <c:axId val="1084542288"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="94707838"/>
+        <c:axId val="1084531472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95963334"/>
+        <c:crossAx val="1084542288"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="95963334"/>
+        <c:axId val="1084542288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1912,128 +2406,1874 @@
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
-            <a:ln w="0">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
               </a:solidFill>
+              <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln w="0">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
             </a:solidFill>
+            <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1084531472"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'3.2'!$B$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'3.2'!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-BF51-49E6-9FF3-350E00310A52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>TREND</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'3.2'!$Q$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'3.2'!$Q$3:$U$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12.825714285714286</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.401428571428571</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.977142857142857</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.552857142857142</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.128571428571428</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-BF51-49E6-9FF3-350E00310A52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>FORECAST</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'3.2'!$Q$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'3.2'!$Q$4:$U$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12.825714285714286</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13.236483516483517</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.842307692307694</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.12925407925408</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.563636363636363</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-BF51-49E6-9FF3-350E00310A52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>GROWTH</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'3.2'!$P$1:$U$1</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'3.2'!$Q$5:$U$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>14.428792338503914</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15.593567345003168</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.852369681298068</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18.212789773607543</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.683030790959588</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-BF51-49E6-9FF3-350E00310A52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1224715200"/>
+        <c:axId val="1224710624"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1224715200"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1224710624"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1224710624"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1224715200"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-                <a:uFillTx/>
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Moving Average</a:t>
+            </a:r>
           </a:p>
-        </c:txPr>
-        <c:crossAx val="94707838"/>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Actual</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A7F4-42AA-AD7E-653B02A8C502}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Forecast</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$A$5:$O$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="0.0">
+                  <c:v>4.4333333333333336</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0">
+                  <c:v>5.333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0">
+                  <c:v>6.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="0.0">
+                  <c:v>7.166666666666667</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="0.0">
+                  <c:v>7.3</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="0.0">
+                  <c:v>8.2666666666666657</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0.0">
+                  <c:v>9.4333333333333318</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="0.0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="0.0">
+                  <c:v>10.199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.0">
+                  <c:v>10.266666666666667</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.0">
+                  <c:v>10.733333333333334</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.0">
+                  <c:v>11.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-A7F4-42AA-AD7E-653B02A8C502}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1222087232"/>
+        <c:axId val="1222089728"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1222087232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Data Point</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1222089728"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1222089728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Value</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1222087232"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
-          </a:solidFill>
-        </a:ln>
-      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
       <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
-              <a:uFillTx/>
-              <a:latin typeface="Arial"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="span"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="0">
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Exponential Smoothing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Actual</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D49B-4B01-9904-335C8C5C882C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Forecast</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$A$21:$O$21</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>4.66</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>4.6879999999999997</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>5.6763999999999992</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>7.1629199999999997</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>6.4888759999999994</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>7.1966627999999995</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>7.8989988399999991</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>8.7396996519999988</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>10.321909895599999</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>10.02657296868</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>9.7979718906039999</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>10.779391567181198</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>11.14381747015436</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D49B-4B01-9904-335C8C5C882C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="853313920"/>
+        <c:axId val="853312256"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="853313920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Data Point</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="853312256"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="853312256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Value</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="853313920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Exponential Smoothing</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Actual</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$B$2:$P$2</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.6999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D4B4-4346-95B8-5818E03F05C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Forecast</c:v>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>'3.3'!$A$37:$O$37</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>3.94</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>4.1680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>4.7475999999999994</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>5.6633199999999988</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>5.8243239999999989</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>6.3270267999999987</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>6.8889187599999975</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>7.5522431319999974</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>8.5865701923999964</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>8.9805991346799967</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>9.1964193942759973</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>9.7974935759931974</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>10.248245503195237</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D4B4-4346-95B8-5818E03F05C9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1438453056"/>
+        <c:axId val="1438453472"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1438453056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Data Point</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1438453472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1438453472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Value</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1438453056"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
 </cs:colorStyle>
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2056,194 +4296,500 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2266,194 +4812,500 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2476,194 +5328,500 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2686,194 +5844,500 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
@@ -2896,204 +6360,1009 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="1">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
   <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPointWireframe>
   <cs:dataTable>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataTable>
   <cs:downBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:downBar>
   <cs:dropLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:dropLine>
   <cs:errorBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:errorBar>
   <cs:floor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMajor>
   <cs:gridlineMinor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:gridlineMinor>
   <cs:hiLoLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:hiLoLine>
   <cs:leaderLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:leaderLine>
   <cs:legend>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:seriesLine>
   <cs:title>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
   </cs:trendline>
   <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:trendlineLabel>
   <cs:upBar>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
   </cs:upBar>
   <cs:valueAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>36000</xdr:colOff>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>36360</xdr:rowOff>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>269280</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>24840</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327660</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE3508BF-828A-4568-B943-D5716B561B1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="36000" y="477000"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3103,27 +7372,33 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>371160</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>77400</xdr:rowOff>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>292680</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>65880</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3E079A2-7266-4910-98DC-635AD5DA23FD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5897520" y="518040"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3133,27 +7408,33 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>57240</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>113400</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>290520</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>111960</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3990DA36-8ECA-4F2C-8A83-12132A339735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="57240" y="3642840"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3163,27 +7444,33 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>352800</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>57240</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name=""/>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22620B72-CCCB-4813-99A8-AC6A26965986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5879160" y="3749040"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3193,27 +7480,33 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>92880</xdr:rowOff>
+      <xdr:colOff>21404</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>15410</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>233280</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>30600</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>338191</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>61644</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name=""/>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0A275FD-FACE-458D-8F91-C1365EF0C20C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="6863400"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3226,83 +7519,386 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B79F6336-C6DA-4E29-9538-AEDC52300783}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6358076F-B543-49A9-BF73-1302F595A747}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>251460</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF6BEAE6-BE90-4C86-976B-8C074D898588}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DF3534D-73E9-4E0C-98DF-0D3222726FAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="LibreOffice">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -3313,7 +7909,13 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -3321,293 +7923,829 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:P45"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5991B573-F784-4EFD-892B-F09A83E171D8}">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="17.399999999999999">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="17.399999999999999">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J2" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="M2" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N2" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="P2" s="2">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD59AF6-ABD7-4739-8544-D8597B2FBA59}">
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="8.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="8.02"/>
+    <col min="16" max="16" width="12.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:21" ht="17.399999999999999">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="n">
+      <c r="B1" s="3">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="n">
+      <c r="C1" s="3">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="n">
+      <c r="D1" s="3">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="n">
+      <c r="E1" s="3">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="n">
+      <c r="F1" s="3">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="n">
+      <c r="G1" s="3">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="n">
+      <c r="H1" s="3">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="n">
+      <c r="I1" s="3">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="n">
+      <c r="J1" s="3">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="n">
+      <c r="K1" s="3">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="n">
+      <c r="L1" s="3">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="n">
+      <c r="M1" s="3">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="n">
+      <c r="N1" s="3">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="n">
+      <c r="O1" s="3">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="n">
+      <c r="P1" s="3">
         <v>15</v>
       </c>
+      <c r="Q1" s="5">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5">
+        <v>19</v>
+      </c>
+      <c r="U1" s="5">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:21" ht="17.399999999999999">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="2">
         <v>3.4</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="2">
         <v>5.2</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>4.7</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2">
         <v>6.1</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="2">
         <v>7.8</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="2">
         <v>6.2</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="2">
         <v>7.5</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J2" s="2">
         <v>9.1</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="2">
         <v>11</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="2">
         <v>9.9</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N2" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="P2" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="18">
+      <c r="P3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>12</v>
+      <c r="Q3" s="8" cm="1">
+        <f t="array" ref="Q3:U3">TREND(B2:P2,B1:P1,Q1:U1)</f>
+        <v>12.825714285714286</v>
+      </c>
+      <c r="R3" s="8">
+        <v>13.401428571428571</v>
+      </c>
+      <c r="S3" s="8">
+        <v>13.977142857142857</v>
+      </c>
+      <c r="T3" s="8">
+        <v>14.552857142857142</v>
+      </c>
+      <c r="U3" s="8">
+        <v>15.128571428571428</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+    <row r="4" spans="1:21" ht="18">
+      <c r="P4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="8">
+        <f>_xlfn.FORECAST.LINEAR(Q1,B2:P2,B1:P1)</f>
+        <v>12.825714285714286</v>
+      </c>
+      <c r="R4" s="8">
+        <f t="shared" ref="R4:U4" si="0">_xlfn.FORECAST.LINEAR(R1,C2:Q2,C1:Q1)</f>
+        <v>13.236483516483517</v>
+      </c>
+      <c r="S4" s="8">
+        <f t="shared" si="0"/>
+        <v>13.842307692307694</v>
+      </c>
+      <c r="T4" s="8">
+        <f t="shared" si="0"/>
+        <v>14.12925407925408</v>
+      </c>
+      <c r="U4" s="8">
+        <f t="shared" si="0"/>
+        <v>14.563636363636363</v>
+      </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+    <row r="5" spans="1:21" ht="18">
+      <c r="K5" s="4"/>
+      <c r="P5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="8" cm="1">
+        <f t="array" ref="Q5:U5">GROWTH(B2:P2,B1:P1,Q1:U1)</f>
+        <v>14.428792338503914</v>
+      </c>
+      <c r="R5" s="8">
+        <v>15.593567345003168</v>
+      </c>
+      <c r="S5" s="8">
+        <v>16.852369681298068</v>
+      </c>
+      <c r="T5" s="8">
+        <v>18.212789773607543</v>
+      </c>
+      <c r="U5" s="8">
+        <v>19.683030790959588</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="6"/>
-    </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="B38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="6"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="B42" s="6"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="6"/>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="6"/>
+    <row r="6" spans="1:21">
+      <c r="K6" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E61C6692-EB05-47D6-BBB0-79278AD19971}">
+  <dimension ref="A1:P38"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:16" ht="17.399999999999999">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="17.399999999999999">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="E2" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="G2" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="J2" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>11</v>
+      </c>
+      <c r="L2" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="M2" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N2" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="O2" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="P2" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="9">
+        <f t="shared" ref="C5:O5" si="0">AVERAGE(B2:D2)</f>
+        <v>4.4333333333333336</v>
+      </c>
+      <c r="D5" s="9">
+        <f t="shared" si="0"/>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="0"/>
+        <v>6.2</v>
+      </c>
+      <c r="F5" s="9">
+        <f t="shared" si="0"/>
+        <v>6.6999999999999993</v>
+      </c>
+      <c r="G5" s="9">
+        <f t="shared" si="0"/>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="H5" s="9">
+        <f t="shared" si="0"/>
+        <v>7.3</v>
+      </c>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
+        <v>8.2666666666666657</v>
+      </c>
+      <c r="J5" s="9">
+        <f t="shared" si="0"/>
+        <v>9.4333333333333318</v>
+      </c>
+      <c r="K5" s="9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L5" s="9">
+        <f t="shared" si="0"/>
+        <v>10.199999999999999</v>
+      </c>
+      <c r="M5" s="9">
+        <f t="shared" si="0"/>
+        <v>10.266666666666667</v>
+      </c>
+      <c r="N5" s="9">
+        <f t="shared" si="0"/>
+        <v>10.733333333333334</v>
+      </c>
+      <c r="O5" s="9">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="e">
+        <f t="shared" ref="E6:O6" si="1">SQRT(SUMXMY2(B4:B6,C5:C7)/3)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="G6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O6" t="e">
+        <f t="shared" si="1"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B21" s="9">
+        <f>B2</f>
+        <v>3.4</v>
+      </c>
+      <c r="C21">
+        <f t="shared" ref="C21:O21" si="2">0.7*C2+0.3*B21</f>
+        <v>4.66</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="2"/>
+        <v>4.6879999999999997</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>5.6763999999999992</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>7.1629199999999997</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="2"/>
+        <v>6.4888759999999994</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="2"/>
+        <v>7.1966627999999995</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>7.8989988399999991</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="2"/>
+        <v>8.7396996519999988</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="2"/>
+        <v>10.321909895599999</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="2"/>
+        <v>10.02657296868</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>9.7979718906039999</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>10.779391567181198</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="2"/>
+        <v>11.14381747015436</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="e">
+        <f t="shared" ref="E22:O22" si="3">SQRT(SUMXMY2(B3:B5,B21:B23)/3)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="G22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O22" t="e">
+        <f t="shared" si="3"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B37" s="9">
+        <f>B2</f>
+        <v>3.4</v>
+      </c>
+      <c r="C37">
+        <f t="shared" ref="C37:O37" si="4">0.3*C2+0.7*B37</f>
+        <v>3.94</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="4"/>
+        <v>4.1680000000000001</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="4"/>
+        <v>4.7475999999999994</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="4"/>
+        <v>5.6633199999999988</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="4"/>
+        <v>5.8243239999999989</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="4"/>
+        <v>6.3270267999999987</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="4"/>
+        <v>6.8889187599999975</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="4"/>
+        <v>7.5522431319999974</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="4"/>
+        <v>8.5865701923999964</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="4"/>
+        <v>8.9805991346799967</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="4"/>
+        <v>9.1964193942759973</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="4"/>
+        <v>9.7974935759931974</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="4"/>
+        <v>10.248245503195237</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="B38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D38" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" t="e">
+        <f t="shared" ref="E38:O38" si="5">SQRT(SUMXMY2(B3:B5,B37:B39)/3)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="F38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="G38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="H38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="I38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O38" t="e">
+        <f t="shared" si="5"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataConsolidate/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>